--- a/Clustering.opdracht/Clustering_logboek.xlsx
+++ b/Clustering.opdracht/Clustering_logboek.xlsx
@@ -1,40 +1,175 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raymo\Documents\DEAI_portfolio\Clustering.opdracht\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA443C5-6F41-458D-A47A-7438976D64DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Logboek" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Logboek" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="30">
+  <si>
+    <t>Features</t>
+  </si>
+  <si>
+    <t>Clusters</t>
+  </si>
+  <si>
+    <t>Scaler</t>
+  </si>
+  <si>
+    <t>Init</t>
+  </si>
+  <si>
+    <t>Max Iter</t>
+  </si>
+  <si>
+    <t>Random State</t>
+  </si>
+  <si>
+    <t>Silhouette</t>
+  </si>
+  <si>
+    <t>Inertia</t>
+  </si>
+  <si>
+    <t>Davies-Bouldin</t>
+  </si>
+  <si>
+    <t>Calinski-Harabasz</t>
+  </si>
+  <si>
+    <t>SalePrice, GrLivArea, Neighborhood</t>
+  </si>
+  <si>
+    <t>Ja</t>
+  </si>
+  <si>
+    <t>random</t>
+  </si>
+  <si>
+    <t>YearBuilt, GarageArea</t>
+  </si>
+  <si>
+    <t>TotalBsmtSF, GrLivArea</t>
+  </si>
+  <si>
+    <t>k-means++</t>
+  </si>
+  <si>
+    <t>Neighborhood, GrLivArea</t>
+  </si>
+  <si>
+    <t>LotArea, GrLivArea</t>
+  </si>
+  <si>
+    <t>OverallQual, Neighborhood, SalePrice</t>
+  </si>
+  <si>
+    <t>Nee</t>
+  </si>
+  <si>
+    <t>OverallQual, SalePrice</t>
+  </si>
+  <si>
+    <t>YearBuilt, SalePrice</t>
+  </si>
+  <si>
+    <t>Neighborhood, SalePrice</t>
+  </si>
+  <si>
+    <t>GarageArea, OverallQual</t>
+  </si>
+  <si>
+    <t>OverallQual, YearBuilt, GrLivArea</t>
+  </si>
+  <si>
+    <t>GrLivArea, SalePrice</t>
+  </si>
+  <si>
+    <t>OverallQual, GarageArea, YearBuilt</t>
+  </si>
+  <si>
+    <t>OverallQual, GrLivArea</t>
+  </si>
+  <si>
+    <t>GrLivArea, YearBuilt, SalePrice</t>
+  </si>
+  <si>
+    <t>Expiriment</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +177,58 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,98 +516,1136 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="42.26953125" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" customWidth="1"/>
+    <col min="5" max="5" width="16.26953125" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Stap</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Opmerkingen</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Dataset inlezen</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AmesHousing.xlsx ingelezen; 2930 rijen, 12 kolommen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Top 3 features kiezen</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Neighborhood, Overall Qual, Gr Liv Area gekozen; Neighborhood is categorie.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Eerste model</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>KMeans met 4 clusters, init k-means++, n_init=10, max_iter=300, StandardScaler toegepast.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Eerste evaluatie</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Eerste modelscore in notebook vastleggen; vergelijk later met experimenten.</t>
-        </is>
-      </c>
+    <row r="1" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2">
+        <v>150</v>
+      </c>
+      <c r="G2" s="2">
+        <v>42</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="I2" s="3">
+        <v>45955</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1.74</v>
+      </c>
+      <c r="K2" s="3">
+        <v>116.7</v>
+      </c>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4">
+        <v>200</v>
+      </c>
+      <c r="G3" s="4">
+        <v>84</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="I3" s="5">
+        <v>47835</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1.756</v>
+      </c>
+      <c r="K3" s="5">
+        <v>69.5</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2">
+        <v>150</v>
+      </c>
+      <c r="G4" s="2">
+        <v>126</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="I4" s="3">
+        <v>49252</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1.724</v>
+      </c>
+      <c r="K4" s="3">
+        <v>105.2</v>
+      </c>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4">
+        <v>100</v>
+      </c>
+      <c r="G5" s="4">
+        <v>168</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="I5" s="5">
+        <v>47841</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1.667</v>
+      </c>
+      <c r="K5" s="5">
+        <v>131.80000000000001</v>
+      </c>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2">
+        <v>200</v>
+      </c>
+      <c r="G6" s="2">
+        <v>210</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="I6" s="3">
+        <v>42032</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1.8859999999999999</v>
+      </c>
+      <c r="K6" s="3">
+        <v>128.30000000000001</v>
+      </c>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4">
+        <v>300</v>
+      </c>
+      <c r="G7" s="4">
+        <v>252</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="I7" s="5">
+        <v>42504</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1.7390000000000001</v>
+      </c>
+      <c r="K7" s="5">
+        <v>99.3</v>
+      </c>
+      <c r="L7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2">
+        <v>200</v>
+      </c>
+      <c r="G8" s="2">
+        <v>294</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="I8" s="3">
+        <v>41659</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1.53</v>
+      </c>
+      <c r="K8" s="3">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="4">
+        <v>150</v>
+      </c>
+      <c r="G9" s="4">
+        <v>336</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.318</v>
+      </c>
+      <c r="I9" s="5">
+        <v>37778</v>
+      </c>
+      <c r="J9" s="5">
+        <v>1.7150000000000001</v>
+      </c>
+      <c r="K9" s="5">
+        <v>112.1</v>
+      </c>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="2">
+        <v>200</v>
+      </c>
+      <c r="G10" s="2">
+        <v>378</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="I10" s="3">
+        <v>38829</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1.5189999999999999</v>
+      </c>
+      <c r="K10" s="3">
+        <v>174.8</v>
+      </c>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="4">
+        <v>9</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="4">
+        <v>300</v>
+      </c>
+      <c r="G11" s="4">
+        <v>420</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="I11" s="5">
+        <v>40853</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1.4610000000000001</v>
+      </c>
+      <c r="K11" s="5">
+        <v>173.9</v>
+      </c>
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="2">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2">
+        <v>300</v>
+      </c>
+      <c r="G12" s="2">
+        <v>462</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="I12" s="3">
+        <v>37902</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1.5409999999999999</v>
+      </c>
+      <c r="K12" s="3">
+        <v>159.9</v>
+      </c>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4">
+        <v>300</v>
+      </c>
+      <c r="G13" s="4">
+        <v>504</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="I13" s="5">
+        <v>35763</v>
+      </c>
+      <c r="J13" s="5">
+        <v>1.72</v>
+      </c>
+      <c r="K13" s="5">
+        <v>189.6</v>
+      </c>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2">
+        <v>300</v>
+      </c>
+      <c r="G14" s="2">
+        <v>546</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="I14" s="3">
+        <v>37709</v>
+      </c>
+      <c r="J14" s="3">
+        <v>1.6870000000000001</v>
+      </c>
+      <c r="K14" s="3">
+        <v>184.1</v>
+      </c>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="4">
+        <v>3</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="4">
+        <v>200</v>
+      </c>
+      <c r="G15" s="4">
+        <v>588</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0.34</v>
+      </c>
+      <c r="I15" s="5">
+        <v>34947</v>
+      </c>
+      <c r="J15" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="K15" s="5">
+        <v>172</v>
+      </c>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="2">
+        <v>200</v>
+      </c>
+      <c r="G16" s="2">
+        <v>630</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="I16" s="3">
+        <v>33353</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1.26</v>
+      </c>
+      <c r="K16" s="3">
+        <v>174.8</v>
+      </c>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="4">
+        <v>7</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="4">
+        <v>200</v>
+      </c>
+      <c r="G17" s="4">
+        <v>672</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="I17" s="5">
+        <v>33302</v>
+      </c>
+      <c r="J17" s="5">
+        <v>1.575</v>
+      </c>
+      <c r="K17" s="5">
+        <v>177.4</v>
+      </c>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2">
+        <v>100</v>
+      </c>
+      <c r="G18" s="2">
+        <v>714</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="I18" s="3">
+        <v>32087</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1.43</v>
+      </c>
+      <c r="K18" s="3">
+        <v>237.2</v>
+      </c>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4">
+        <v>4</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="4">
+        <v>150</v>
+      </c>
+      <c r="G19" s="4">
+        <v>756</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="I19" s="5">
+        <v>26736</v>
+      </c>
+      <c r="J19" s="5">
+        <v>1.347</v>
+      </c>
+      <c r="K19" s="5">
+        <v>235</v>
+      </c>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2">
+        <v>150</v>
+      </c>
+      <c r="G20" s="2">
+        <v>798</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.52700000000000002</v>
+      </c>
+      <c r="I20" s="3">
+        <v>24964</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1.3819999999999999</v>
+      </c>
+      <c r="K20" s="3">
+        <v>257.3</v>
+      </c>
+      <c r="L20" s="1"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="4">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="4">
+        <v>200</v>
+      </c>
+      <c r="G21" s="4">
+        <v>840</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0.495</v>
+      </c>
+      <c r="I21" s="5">
+        <v>27798</v>
+      </c>
+      <c r="J21" s="5">
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="K21" s="5">
+        <v>213.5</v>
+      </c>
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="2">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="2">
+        <v>150</v>
+      </c>
+      <c r="G22" s="2">
+        <v>882</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="I22" s="3">
+        <v>28439</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1.45</v>
+      </c>
+      <c r="K22" s="3">
+        <v>278.7</v>
+      </c>
+      <c r="L22" s="1"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="4">
+        <v>10</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="4">
+        <v>200</v>
+      </c>
+      <c r="G23" s="4">
+        <v>924</v>
+      </c>
+      <c r="H23" s="5">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="I23" s="5">
+        <v>25498</v>
+      </c>
+      <c r="J23" s="5">
+        <v>1.228</v>
+      </c>
+      <c r="K23" s="5">
+        <v>277.89999999999998</v>
+      </c>
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="2">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="2">
+        <v>300</v>
+      </c>
+      <c r="G24" s="2">
+        <v>966</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="I24" s="3">
+        <v>25536</v>
+      </c>
+      <c r="J24" s="3">
+        <v>1.3380000000000001</v>
+      </c>
+      <c r="K24" s="3">
+        <v>272</v>
+      </c>
+      <c r="L24" s="1"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="4">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="4">
+        <v>100</v>
+      </c>
+      <c r="G25" s="4">
+        <v>1008</v>
+      </c>
+      <c r="H25" s="5">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="I25" s="5">
+        <v>21590</v>
+      </c>
+      <c r="J25" s="5">
+        <v>1.246</v>
+      </c>
+      <c r="K25" s="5">
+        <v>280.3</v>
+      </c>
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="2">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="2">
+        <v>100</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1050</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="I26" s="3">
+        <v>22402</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1.214</v>
+      </c>
+      <c r="K26" s="3">
+        <v>308.8</v>
+      </c>
+      <c r="L26" s="1"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="4">
+        <v>7</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="4">
+        <v>300</v>
+      </c>
+      <c r="G27" s="4">
+        <v>1092</v>
+      </c>
+      <c r="H27" s="5">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="I27" s="5">
+        <v>20448</v>
+      </c>
+      <c r="J27" s="5">
+        <v>1.147</v>
+      </c>
+      <c r="K27" s="5">
+        <v>307.8</v>
+      </c>
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="2">
+        <v>6</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="2">
+        <v>150</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1134</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="I28" s="3">
+        <v>18115</v>
+      </c>
+      <c r="J28" s="3">
+        <v>1.278</v>
+      </c>
+      <c r="K28" s="3">
+        <v>287.2</v>
+      </c>
+      <c r="L28" s="1"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="4">
+        <v>3</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="4">
+        <v>300</v>
+      </c>
+      <c r="G29" s="4">
+        <v>1176</v>
+      </c>
+      <c r="H29" s="5">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="I29" s="5">
+        <v>15399</v>
+      </c>
+      <c r="J29" s="5">
+        <v>1.2210000000000001</v>
+      </c>
+      <c r="K29" s="5">
+        <v>328</v>
+      </c>
+      <c r="L29" s="1"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="2">
+        <v>3</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="2">
+        <v>300</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1218</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0.626</v>
+      </c>
+      <c r="I30" s="3">
+        <v>16730</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="K30" s="3">
+        <v>315.89999999999998</v>
+      </c>
+      <c r="L30" s="1"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="4">
+        <v>4</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="4">
+        <v>200</v>
+      </c>
+      <c r="G31" s="4">
+        <v>1260</v>
+      </c>
+      <c r="H31" s="5">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="I31" s="5">
+        <v>13520</v>
+      </c>
+      <c r="J31" s="5">
+        <v>0.96099999999999997</v>
+      </c>
+      <c r="K31" s="5">
+        <v>291</v>
+      </c>
+      <c r="L31" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
